--- a/C#/Assessment2/Part2/2DShapeCalculator_TestReport_Units and System.xlsx
+++ b/C#/Assessment2/Part2/2DShapeCalculator_TestReport_Units and System.xlsx
@@ -5,12 +5,12 @@
   <workbookPr checkCompatibility="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Holmesglen - Certificate IV\certificate-4\C#\Assessment2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Holmesglen - Certificate IV\certificate-4\C#\Assessment2\Part2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71DEADA-932A-4C83-845F-0C4D48F787CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D04954-19DD-4B01-9180-10D97777CAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Info" sheetId="1" r:id="rId1"/>
@@ -1447,162 +1447,6 @@
     <xf numFmtId="4" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1626,6 +1470,162 @@
     </xf>
     <xf numFmtId="4" fontId="20" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4880,25 +4880,25 @@
   <sheetData>
     <row r="1" spans="2:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="2"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="2" spans="2:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
     </row>
     <row r="3" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="3"/>
-      <c r="C3" s="98" t="s">
+      <c r="C3" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="2:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3"/>
@@ -4910,52 +4910,52 @@
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="109" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="C7" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="114"/>
     </row>
     <row r="8" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="104"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114"/>
     </row>
     <row r="9" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="105">
+      <c r="C9" s="115">
         <v>45795</v>
       </c>
-      <c r="D9" s="105"/>
-      <c r="E9" s="106"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="116"/>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="107" t="s">
+      <c r="C10" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="107"/>
-      <c r="E10" s="108"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="118"/>
     </row>
     <row r="11" spans="2:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B11" s="5"/>
@@ -4974,10 +4974,10 @@
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="2:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="102"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="102"/>
+      <c r="B14" s="112"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5020,64 +5020,64 @@
   <sheetData>
     <row r="1" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:11" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
     </row>
     <row r="3" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
       <c r="F4" s="18">
         <v>42</v>
       </c>
       <c r="G4" s="19"/>
     </row>
     <row r="5" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="122"/>
-      <c r="C5" s="129" t="s">
+      <c r="B5" s="140"/>
+      <c r="C5" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="130"/>
-      <c r="E5" s="131"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="20">
         <v>0</v>
       </c>
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="2:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="122"/>
-      <c r="C6" s="123" t="s">
+      <c r="B6" s="140"/>
+      <c r="C6" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
       <c r="G6" s="22">
         <f>F4+F5</f>
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="124" t="s">
+      <c r="B7" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
       <c r="G7" s="23">
         <v>0</v>
       </c>
@@ -5085,13 +5085,13 @@
       <c r="K7" s="24"/>
     </row>
     <row r="8" spans="2:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
       <c r="G8" s="25">
         <f>SUM(G6:G7)</f>
         <v>42</v>
@@ -5339,38 +5339,38 @@
     <row r="20" spans="2:12" s="30" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="2:12" s="30" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:12" s="30" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="110" t="s">
+      <c r="C22" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="115" t="s">
+      <c r="D22" s="131"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="115" t="s">
+      <c r="G22" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="117" t="s">
+      <c r="H22" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="117" t="s">
+      <c r="I22" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="117" t="s">
+      <c r="J22" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="117" t="s">
+      <c r="K22" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="L22" s="132" t="s">
+      <c r="L22" s="127" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:12" s="30" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="114"/>
+      <c r="B23" s="134"/>
       <c r="C23" s="36" t="s">
         <v>22</v>
       </c>
@@ -5380,13 +5380,13 @@
       <c r="E23" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="116"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="133"/>
+      <c r="F23" s="136"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="128"/>
     </row>
     <row r="24" spans="2:12" s="30" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="37"/>
@@ -6226,12 +6226,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="J22:J23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="I22:I23"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="B22:B23"/>
@@ -6242,8 +6236,14 @@
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="I22:I23"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" sqref="G24:H24 G25" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"High, Medium, Low"</formula1>
     </dataValidation>
@@ -6279,64 +6279,64 @@
   <sheetData>
     <row r="1" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:11" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
     </row>
     <row r="3" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
       <c r="F4" s="18">
         <v>22</v>
       </c>
       <c r="G4" s="19"/>
     </row>
     <row r="5" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="122"/>
-      <c r="C5" s="129" t="s">
+      <c r="B5" s="140"/>
+      <c r="C5" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="130"/>
-      <c r="E5" s="131"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="20">
         <v>0</v>
       </c>
       <c r="G5" s="21"/>
     </row>
     <row r="6" spans="2:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="122"/>
-      <c r="C6" s="123" t="s">
+      <c r="B6" s="140"/>
+      <c r="C6" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
       <c r="G6" s="22">
         <f>F4+F5</f>
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="124" t="s">
+      <c r="B7" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
       <c r="G7" s="23">
         <v>0</v>
       </c>
@@ -6344,13 +6344,13 @@
       <c r="K7" s="24"/>
     </row>
     <row r="8" spans="2:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
       <c r="G8" s="25">
         <f>SUM(G6:G7)</f>
         <v>22</v>
@@ -6477,38 +6477,38 @@
     </row>
     <row r="17" spans="2:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="138" t="s">
+      <c r="B18" s="151" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="140" t="s">
+      <c r="C18" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="141"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="143" t="s">
+      <c r="D18" s="154"/>
+      <c r="E18" s="155"/>
+      <c r="F18" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="143" t="s">
+      <c r="G18" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="134" t="s">
+      <c r="H18" s="147" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="134" t="s">
+      <c r="I18" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="134" t="s">
+      <c r="J18" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="134" t="s">
+      <c r="K18" s="147" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="136" t="s">
+      <c r="L18" s="149" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="139"/>
+      <c r="B19" s="152"/>
       <c r="C19" s="91" t="s">
         <v>22</v>
       </c>
@@ -6518,13 +6518,13 @@
       <c r="E19" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="135"/>
-      <c r="L19" s="137"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="148"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="148"/>
+      <c r="K19" s="148"/>
+      <c r="L19" s="150"/>
     </row>
     <row r="20" spans="2:12" s="92" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="37"/>
@@ -6574,56 +6574,56 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="149">
+      <c r="B24" s="97">
         <v>1</v>
       </c>
-      <c r="C24" s="150" t="s">
+      <c r="C24" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="150">
+      <c r="D24" s="98">
         <v>5</v>
       </c>
-      <c r="E24" s="150">
+      <c r="E24" s="98">
         <v>25</v>
       </c>
-      <c r="F24" s="150"/>
-      <c r="G24" s="151" t="s">
+      <c r="F24" s="98"/>
+      <c r="G24" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="386.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="149">
+      <c r="B25" s="97">
         <v>2</v>
       </c>
-      <c r="C25" s="150" t="s">
+      <c r="C25" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="150">
+      <c r="D25" s="98">
         <v>5</v>
       </c>
-      <c r="E25" s="150">
+      <c r="E25" s="98">
         <v>20</v>
       </c>
-      <c r="F25" s="150"/>
-      <c r="G25" s="151" t="s">
+      <c r="F25" s="98"/>
+      <c r="G25" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="198.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="149">
+      <c r="B26" s="97">
         <v>3</v>
       </c>
-      <c r="C26" s="150" t="s">
+      <c r="C26" s="98" t="s">
         <v>110</v>
       </c>
-      <c r="D26" s="150">
+      <c r="D26" s="98">
         <v>-1</v>
       </c>
-      <c r="E26" s="150" t="s">
+      <c r="E26" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="F26" s="150"/>
-      <c r="G26" s="151" t="s">
+      <c r="F26" s="98"/>
+      <c r="G26" s="99" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6700,58 +6700,58 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="388.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="149">
+      <c r="B31" s="97">
         <v>8</v>
       </c>
-      <c r="C31" s="150" t="s">
+      <c r="C31" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="150">
+      <c r="D31" s="98">
         <v>5</v>
       </c>
-      <c r="E31" s="157">
+      <c r="E31" s="105">
         <f>PI()*5*5</f>
         <v>78.539816339744831</v>
       </c>
-      <c r="F31" s="150"/>
-      <c r="G31" s="151" t="s">
+      <c r="F31" s="98"/>
+      <c r="G31" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="384.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="149">
+      <c r="B32" s="97">
         <v>9</v>
       </c>
-      <c r="C32" s="150" t="s">
+      <c r="C32" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="150">
+      <c r="D32" s="98">
         <v>5</v>
       </c>
-      <c r="E32" s="157">
+      <c r="E32" s="105">
         <f>PI()*2*5</f>
         <v>31.415926535897931</v>
       </c>
-      <c r="F32" s="150"/>
-      <c r="G32" s="151" t="s">
+      <c r="F32" s="98"/>
+      <c r="G32" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="204.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="149">
+      <c r="B33" s="97">
         <v>10</v>
       </c>
-      <c r="C33" s="150" t="s">
+      <c r="C33" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="150">
+      <c r="D33" s="98">
         <v>-1</v>
       </c>
-      <c r="E33" s="150" t="s">
+      <c r="E33" s="98" t="s">
         <v>111</v>
       </c>
-      <c r="F33" s="150"/>
-      <c r="G33" s="151" t="s">
+      <c r="F33" s="98"/>
+      <c r="G33" s="99" t="s">
         <v>69</v>
       </c>
     </row>
@@ -6806,188 +6806,189 @@
       <c r="E36" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="F36" s="148"/>
+      <c r="F36" s="96"/>
       <c r="G36" s="82" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="146">
+      <c r="B37" s="145">
         <v>14</v>
       </c>
-      <c r="C37" s="145" t="s">
+      <c r="C37" s="144" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="145" t="s">
+      <c r="D37" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="145" t="s">
+      <c r="E37" s="144" t="s">
         <v>105</v>
       </c>
-      <c r="F37" s="148"/>
-      <c r="G37" s="147" t="s">
+      <c r="F37" s="96"/>
+      <c r="G37" s="146" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="146"/>
-      <c r="C38" s="145"/>
-      <c r="D38" s="145"/>
-      <c r="E38" s="145"/>
-      <c r="F38" s="148"/>
-      <c r="G38" s="147"/>
+      <c r="B38" s="145"/>
+      <c r="C38" s="144"/>
+      <c r="D38" s="144"/>
+      <c r="E38" s="144"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="146"/>
     </row>
     <row r="39" spans="2:7" ht="174.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="149">
+      <c r="B39" s="97">
         <v>15</v>
       </c>
-      <c r="C39" s="150" t="s">
+      <c r="C39" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="150">
+      <c r="D39" s="98">
         <v>0</v>
       </c>
-      <c r="E39" s="150" t="s">
+      <c r="E39" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="150"/>
-      <c r="G39" s="151" t="s">
+      <c r="F39" s="98"/>
+      <c r="G39" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="174.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="149">
+      <c r="B40" s="97">
         <v>16</v>
       </c>
-      <c r="C40" s="150" t="s">
+      <c r="C40" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="150" t="s">
+      <c r="D40" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="E40" s="150" t="s">
+      <c r="E40" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="150"/>
-      <c r="G40" s="151" t="s">
+      <c r="F40" s="98"/>
+      <c r="G40" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="174.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="149">
+      <c r="B41" s="97">
         <v>17</v>
       </c>
-      <c r="C41" s="150" t="s">
+      <c r="C41" s="98" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="150">
+      <c r="D41" s="98">
         <v>6</v>
       </c>
-      <c r="E41" s="150" t="s">
+      <c r="E41" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="F41" s="150"/>
-      <c r="G41" s="151" t="s">
+      <c r="F41" s="98"/>
+      <c r="G41" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="149">
+      <c r="B42" s="97">
         <v>18</v>
       </c>
-      <c r="C42" s="150" t="s">
+      <c r="C42" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="150">
+      <c r="D42" s="98">
         <v>0</v>
       </c>
-      <c r="E42" s="150" t="s">
+      <c r="E42" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="152"/>
-      <c r="G42" s="151" t="s">
+      <c r="F42" s="100"/>
+      <c r="G42" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="149">
+      <c r="B43" s="97">
         <v>19</v>
       </c>
-      <c r="C43" s="150" t="s">
+      <c r="C43" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="D43" s="150">
+      <c r="D43" s="98">
         <v>4</v>
       </c>
-      <c r="E43" s="150" t="s">
+      <c r="E43" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="152"/>
-      <c r="G43" s="151" t="s">
+      <c r="F43" s="100"/>
+      <c r="G43" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="149">
+      <c r="B44" s="97">
         <v>20</v>
       </c>
-      <c r="C44" s="150" t="s">
+      <c r="C44" s="98" t="s">
         <v>103</v>
       </c>
-      <c r="D44" s="150" t="s">
+      <c r="D44" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="E44" s="150" t="s">
+      <c r="E44" s="98" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="152"/>
-      <c r="G44" s="151" t="s">
+      <c r="F44" s="100"/>
+      <c r="G44" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="257.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="149">
+      <c r="B45" s="97">
         <v>21</v>
       </c>
-      <c r="C45" s="150" t="s">
+      <c r="C45" s="98" t="s">
         <v>108</v>
       </c>
-      <c r="D45" s="150">
+      <c r="D45" s="98">
         <v>5</v>
       </c>
-      <c r="E45" s="150" t="s">
+      <c r="E45" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="F45" s="152"/>
-      <c r="G45" s="151" t="s">
+      <c r="F45" s="100"/>
+      <c r="G45" s="99" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="409.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="153">
+      <c r="B46" s="101">
         <v>22</v>
       </c>
-      <c r="C46" s="154" t="s">
+      <c r="C46" s="102" t="s">
         <v>107</v>
       </c>
-      <c r="D46" s="154">
+      <c r="D46" s="102">
         <v>3</v>
       </c>
-      <c r="E46" s="154" t="s">
+      <c r="E46" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="F46" s="155"/>
-      <c r="G46" s="156" t="s">
+      <c r="F46" s="103"/>
+      <c r="G46" s="104" t="s">
         <v>69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:F6"/>
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="J18:J19"/>
     <mergeCell ref="K18:K19"/>
@@ -6998,12 +6999,11 @@
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="H18:H19"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="G37:G38"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" sqref="G20:H20 G21" xr:uid="{375DB3CC-9A30-4284-A7FE-88B2ABA838E5}">
